--- a/excel/Batch_05_Leads_Tracker.xlsx
+++ b/excel/Batch_05_Leads_Tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Leads Tracker" sheetId="1" r:id="rId1"/>
+    <sheet name="Leads" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -418,145 +418,84 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="32.83203125" customWidth="1"/>
-    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Batch 05 Lawyers Leads Tracker</v>
+        <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v/>
+        <v>Website</v>
       </c>
       <c r="C1" t="str">
-        <v/>
+        <v>Email</v>
       </c>
       <c r="D1" t="str">
-        <v/>
+        <v>Phone</v>
       </c>
       <c r="E1" t="str">
-        <v/>
+        <v>Social Links</v>
       </c>
       <c r="F1" t="str">
-        <v/>
+        <v>1st Email Subject</v>
       </c>
       <c r="G1" t="str">
-        <v/>
+        <v>1st Email</v>
       </c>
       <c r="H1" t="str">
-        <v/>
+        <v>Status</v>
       </c>
       <c r="I1" t="str">
-        <v/>
+        <v>Dates</v>
       </c>
       <c r="J1" t="str">
-        <v/>
+        <v>Follow Up 1 Subject</v>
       </c>
       <c r="K1" t="str">
-        <v/>
+        <v>Follow Up 1</v>
       </c>
       <c r="L1" t="str">
-        <v/>
+        <v>Status</v>
       </c>
       <c r="M1" t="str">
-        <v/>
+        <v>Dates</v>
       </c>
       <c r="N1" t="str">
-        <v/>
+        <v>Follow Up 2 Subject</v>
       </c>
       <c r="O1" t="str">
-        <v/>
+        <v>Follow Up 2</v>
       </c>
       <c r="P1" t="str">
-        <v/>
+        <v>Status</v>
       </c>
       <c r="Q1" t="str">
-        <v/>
+        <v>Dates</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Lead Status</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Name</v>
+        <v>R.O.C.K Solicitors</v>
       </c>
       <c r="B2" t="str">
-        <v>Website</v>
+        <v>https://www.rocksolicitors.com/</v>
       </c>
       <c r="C2" t="str">
-        <v>Email</v>
+        <v>enquiries@rocksolicitors.com</v>
       </c>
       <c r="D2" t="str">
-        <v>Phone</v>
+        <v>020 8673 5819; emergency 07578 581877</v>
       </c>
       <c r="E2" t="str">
-        <v>Social Links</v>
+        <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=426103</v>
       </c>
       <c r="F2" t="str">
-        <v>1st Email Subject</v>
-      </c>
-      <c r="G2" t="str">
-        <v>1st Email</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Status</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Dates</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Follow Up 1 Subject</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Follow Up 1</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Status</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Dates</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Follow Up 2 Subject</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Follow Up 2</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Status</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>Dates</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Lead Status</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Verification / Notes</v>
-      </c>
-      <c r="T2" t="str">
-        <v>Sources</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>R.O.C.K Solicitors</v>
-      </c>
-      <c r="B3" t="str">
-        <v>https://www.rocksolicitors.com/</v>
-      </c>
-      <c r="C3" t="str">
-        <v>enquiries@rocksolicitors.com</v>
-      </c>
-      <c r="D3" t="str">
-        <v>020 8673 5819; emergency 07578 581877</v>
-      </c>
-      <c r="E3" t="str">
-        <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=426103</v>
-      </c>
-      <c r="F3" t="str">
         <v>Homepage redesign concept for R.O.C.K Solicitors</v>
       </c>
-      <c r="G3" t="str" xml:space="preserve">
+      <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R.O.C.K Solicitors team,
 I found R.O.C.K Solicitors while researching established London law firms. Your broad mix of family, immigration, conveyancing, education and public-law services gives local clients one firm to turn to.
 After reviewing the current website, I noticed that the site still uses an older .aspx structure, repeats long department and contact blocks on each page, links to the discontinued Google+ network, and shows a 2016–2023 footer. On mobile, urgent visitors must work through repeated navigation before they can identify the right department or contact the firm.
@@ -567,16 +506,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
+      <c r="H2" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J2" t="str">
         <v>Following up on the R.O.C.K Solicitors website concept</v>
       </c>
-      <c r="K3" t="str" xml:space="preserve">
+      <c r="K2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R.O.C.K Solicitors team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a concise practice-area gateway, a persistent call and emergency action, named solicitor profiles, current trust information and a shorter enquiry journey. This would directly address the current issue: the site still uses an older .aspx structure, repeats long department and contact blocks on each page, links to the discontinued Google+ network, and shows a 2016–2023 footer.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -584,62 +523,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v>Final follow-up — R.O.C.K Solicitors website concept</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
+      <c r="O2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R.O.C.K Solicitors team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S3" t="str">
-        <v>High redesign need. Live official site and current SRA-regulated firm. Email is published on the official contact page and matches the domain; mailbox acceptance not SMTP-tested.</v>
-      </c>
-      <c r="T3" t="str">
-        <v>https://www.rocksolicitors.com/contact-us.aspx | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=426103</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
         <v>Pearl &amp; Co Solicitors</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B3" t="str">
         <v>https://www.pearlandcosolicitors.co.uk/</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C3" t="str">
         <v>david@pearlandco.co.uk</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D3" t="str">
         <v>020 8202 6202</v>
       </c>
-      <c r="E4" t="str">
-        <v>Facebook: https://www.facebook.com/p/Pearl-Co-Solicitors-100071180778023/ | Law Society: https://solicitors.lawsociety.org.uk/office/542768/pearl-co</v>
-      </c>
-      <c r="F4" t="str">
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facebook: https://www.facebook.com/p/Pearl-Co-Solicitors-100071180778023/
+Facebook: https://solicitors.lawsociety.org.uk/office/542768/pearl-co</v>
+      </c>
+      <c r="F3" t="str">
         <v>Homepage redesign concept for Pearl &amp; Co Solicitors</v>
       </c>
-      <c r="G4" t="str" xml:space="preserve">
+      <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi David,
 I found Pearl &amp; Co Solicitors while researching established London law firms. The firm’s partner-led service and long-standing work for London and the Home Counties are strong reasons for clients to choose a smaller practice.
 After reviewing the current website, I noticed that the homepage gives visitors a very brief, generic introduction and does not quickly explain the partners’ expertise, the matters handled or what happens after an enquiry. A prospective client comparing several firms may leave without seeing why Pearl &amp; Co is the safer or more personal choice.
@@ -650,16 +586,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
+      <c r="H3" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J3" t="str">
         <v>Following up on the Pearl &amp; Co Solicitors website concept</v>
       </c>
-      <c r="K4" t="str" xml:space="preserve">
+      <c r="K3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi David,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a clearer service-led hero, visible partner profiles, practical matter guides, testimonials and a consultation action beside each key practice area. This would directly address the current issue: the homepage gives visitors a very brief, generic introduction and does not quickly explain the partners’ expertise, the matters handled or what happens after an enquiry.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -667,62 +603,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v>Final follow-up — Pearl &amp; Co Solicitors website concept</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
+      <c r="O3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi David,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S4" t="str">
-        <v>High reply potential because a named partner email is published by the firm. Live site and current regulated listing. Mailbox acceptance not SMTP-tested.</v>
-      </c>
-      <c r="T4" t="str">
-        <v>https://www.pearlandcosolicitors.co.uk/contact/ | https://solicitors.lawsociety.org.uk/office/542768/pearl-co</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
         <v>A.T. Law</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B4" t="str">
         <v>https://www.atlaw.org.uk/</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C4" t="str">
         <v>archin@atlaw.org.uk</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D4" t="str">
         <v>020 8868 2173; mobile 07958 900777</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E4" t="str">
         <v>Official profile: https://www.atlaw.org.uk/Profile.html</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F4" t="str">
         <v>Homepage redesign concept for A.T. Law</v>
       </c>
-      <c r="G5" t="str" xml:space="preserve">
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Archin,
 I found A.T. Law while researching established London law firms. Your direct, founder-led approach and flexible fee information can reassure clients who want personal attention.
 After reviewing the current website, I noticed that the static site still follows an older menu structure built around Firm Overview, Profile, Expertise and Fee Structure, with limited visual hierarchy or an obvious consultation path. Visitors must interpret firm-centred labels before they can tell whether you handle their problem, which can reduce calls from mobile users.
@@ -733,16 +665,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
+      <c r="H4" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J4" t="str">
         <v>Following up on the A.T. Law website concept</v>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="K4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Archin,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are client-focused practice-area choices, a prominent call or WhatsApp action, a short ‘how I can help’ section, clear fee expectations and a streamlined contact form. This would directly address the current issue: the static site still follows an older menu structure built around Firm Overview, Profile, Expertise and Fee Structure, with limited visual hierarchy or an obvious consultation path.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -750,62 +682,60 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>Final follow-up — A.T. Law website concept</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
+      <c r="O4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Archin,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S5" t="str">
-        <v>High reply potential because the public email is named and domain-matched. Live official site; regulator status should be checked again immediately before sending. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T5" t="str">
-        <v>https://www.atlaw.org.uk/ | https://www.atlaw.org.uk/Complaints.html</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
         <v>Douglass Simon Solicitors</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B5" t="str">
         <v>https://www.douglass-simon.com/</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C5" t="str">
         <v>info@douglass-simon.com</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D5" t="str">
         <v>020 3375 0555</v>
       </c>
-      <c r="E6" t="str">
-        <v>Facebook: https://www.facebook.com/douglasssimonsolicitors/ | Instagram: https://www.instagram.com/douglasssimonsolicitors/ | SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=670776</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facebook: https://www.facebook.com/douglasssimonsolicitors/
+Facebook: https://www.instagram.com/douglasssimonsolicitors/
+Facebook: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=670776</v>
+      </c>
+      <c r="F5" t="str">
         <v>Homepage redesign concept for Douglass Simon Solicitors</v>
       </c>
-      <c r="G6" t="str" xml:space="preserve">
+      <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Douglass Simon Solicitors team,
 I found Douglass Simon Solicitors while researching established London law firms. Your immigration, family, employment, wills and commercial experience gives the firm a useful cross-border and private-client story.
 After reviewing the current website, I noticed that the homepage duplicates menu and welcome elements, carries a long navigation list and gives limited priority to the enquiry action. The repeated structure makes the site feel harder to scan and can hide the firm’s strongest services and people from visitors making a quick decision.
@@ -816,16 +746,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
+      <c r="H5" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J5" t="str">
         <v>Following up on the Douglass Simon Solicitors website concept</v>
       </c>
-      <c r="K6" t="str" xml:space="preserve">
+      <c r="K5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Douglass Simon Solicitors team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are one focused navigation, clear service pathways, stronger solicitor profiles, current client proof and a short consultation form. This would directly address the current issue: the homepage duplicates menu and welcome elements, carries a long navigation list and gives limited priority to the enquiry action.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -833,62 +763,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v>Final follow-up — Douglass Simon Solicitors website concept</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
+      <c r="O5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Douglass Simon Solicitors team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S6" t="str">
-        <v>Medium reply potential: active SRA-regulated sole practice and active social presence, but general inbox. Official email/domain match; mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T6" t="str">
-        <v>https://www.douglass-simon.com/contact-us/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=670776 | https://www.facebook.com/douglasssimonsolicitors/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str">
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
         <v>Mono Law</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B6" t="str">
         <v>https://monolaw.co.uk/</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C6" t="str">
         <v>info@monolaw.co.uk</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D6" t="str">
         <v>020 3893 3066</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E6" t="str">
         <v>Law Society: https://solicitors.lawsociety.org.uk/office/603117/mono-law-limited</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F6" t="str">
         <v>Homepage redesign concept for Mono Law</v>
       </c>
-      <c r="G7" t="str" xml:space="preserve">
+      <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Mono Law team,
 I found Mono Law while researching established London law firms. Your London practice covers important personal and business matters that benefit from clear, reassuring explanations.
 After reviewing the current website, I noticed that the site still displays a 2017 copyright, an ‘Our Website Launch’ item from August 2017 as a recent post, an empty Twitter-updates area and repeated sidebar content. Those stale elements can make an otherwise active regulated firm look unattended and may weaken confidence before a client enquires.
@@ -899,16 +825,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
+      <c r="H6" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J6" t="str">
         <v>Following up on the Mono Law website concept</v>
       </c>
-      <c r="K7" t="str" xml:space="preserve">
+      <c r="K6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Mono Law team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a current service-led homepage, recent insights or no empty feed at all, visible lawyer credentials, trust markers and a simple consultation flow. This would directly address the current issue: the site still displays a 2017 copyright, an ‘Our Website Launch’ item from August 2017 as a recent post, an empty Twitter-updates area and repeated sidebar content.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -916,62 +842,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v>Final follow-up — Mono Law website concept</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
+      <c r="O6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Mono Law team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S7" t="str">
-        <v>High redesign need. Public official email matches domain; SRA/Law Society record confirms firm identity. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T7" t="str">
-        <v>https://monolaw.co.uk/contact-us/ | https://solicitors.lawsociety.org.uk/office/603117/mono-law-limited</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str">
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
         <v>Ties Solicitors</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B7" t="str">
         <v>https://www.tiessolicitors.co.uk/</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C7" t="str">
         <v>bunmi@tiessolicitors.co.uk</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D7" t="str">
         <v>020 8885 0208; out of hours 07930 279016</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E7" t="str">
         <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=640869</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F7" t="str">
         <v>Homepage redesign concept for Ties Solicitors</v>
       </c>
-      <c r="G8" t="str" xml:space="preserve">
+      <c r="G7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bunmi,
 I found Ties Solicitors while researching established London law firms. Your partner-led team and broad work across conveyancing, family, crime, immigration and probate are strong local trust signals.
 After reviewing the current website, I noticed that the homepage contains several spelling and grammar errors, very long service descriptions and an outdated SRA number that conflicts with the current SRA register. For a regulated service, inconsistent regulatory information and unpolished copy can create unnecessary doubt at the exact point a client is deciding whom to trust.
@@ -982,16 +904,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
+      <c r="H7" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J7" t="str">
         <v>Following up on the Ties Solicitors website concept</v>
       </c>
-      <c r="K8" t="str" xml:space="preserve">
+      <c r="K7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bunmi,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are correct current regulatory details, concise service cards, prominent partner profiles, a clear out-of-hours route and an accessible consultation form. This would directly address the current issue: the homepage contains several spelling and grammar errors, very long service descriptions and an outdated SRA number that conflicts with the current SRA register.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -999,62 +921,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v>Final follow-up — Ties Solicitors website concept</v>
       </c>
-      <c r="O8" t="str" xml:space="preserve">
+      <c r="O7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bunmi,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S8" t="str">
-        <v>High reply potential due to named SRA-listed contact. Important: website shows SRA 300468 while current SRA listing is 640869; phrase carefully as a consistency check, not an accusation. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T8" t="str">
-        <v>https://www.tiessolicitors.co.uk/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=640869</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
         <v>Tice Madox</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B8" t="str">
         <v>https://ticemadox.com/</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C8" t="str">
         <v>enquiries@ticemadox.com</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D8" t="str">
         <v>020 8553 2173; emergency 07931 727597</v>
       </c>
-      <c r="E9" t="str">
-        <v>X: https://x.com/tice_madox | SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=802485</v>
-      </c>
-      <c r="F9" t="str">
+      <c r="E8" t="str" xml:space="preserve">
+        <v xml:space="preserve">X: https://x.com/tice_madox
+X: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=802485</v>
+      </c>
+      <c r="F8" t="str">
         <v>Homepage redesign concept for Tice Madox</v>
       </c>
-      <c r="G9" t="str" xml:space="preserve">
+      <c r="G8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Tice Madox team,
 I found Tice Madox while researching established London law firms. Your work across criminal, immigration, family, employment and commercial matters gives the firm a distinctive full-service position.
 After reviewing the current website, I noticed that the homepage uses long, repetitive prose, awkward phrases such as ‘two folds,’ and an obsolete Google+ link alongside current social channels. Clients dealing with urgent or stressful legal problems may struggle to identify the relevant service and the fastest next step.
@@ -1065,16 +984,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
+      <c r="H8" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J8" t="str">
         <v>Following up on the Tice Madox website concept</v>
       </c>
-      <c r="K9" t="str" xml:space="preserve">
+      <c r="K8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Tice Madox team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are plain-language service pathways, a visible 24-hour contact action, concise case-type explanations, current solicitor profiles and a shorter enquiry section. This would directly address the current issue: the homepage uses long, repetitive prose, awkward phrases such as ‘two folds,’ and an obsolete Google+ link alongside current social channels.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1082,62 +1001,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>Final follow-up — Tice Madox website concept</v>
       </c>
-      <c r="O9" t="str" xml:space="preserve">
+      <c r="O8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Tice Madox team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S9" t="str">
-        <v>High redesign need. Live site, current SRA number shown and recent X activity found. Public domain email; mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T9" t="str">
-        <v>https://ticemadox.com/ | https://ticemadox.com/contact/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=802485 | https://x.com/tice_madox</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
         <v>Nandy &amp; Co Solicitors</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B9" t="str">
         <v>https://nandyandco.co.uk/</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C9" t="str">
         <v>info@nandysolicitors.co.uk</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D9" t="str">
         <v>020 8536 1800</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E9" t="str">
         <v>SRA details on official site: https://nandyandco.co.uk/privacy-and-cookie-policy/</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F9" t="str">
         <v>Homepage redesign concept for Nandy &amp; Co Solicitors</v>
       </c>
-      <c r="G10" t="str" xml:space="preserve">
+      <c r="G9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Nandy &amp; Co team,
 I found Nandy &amp; Co Solicitors while researching established London law firms. Your immigration, asylum and civil-law experience serves clients who need confidence and very clear guidance.
 After reviewing the current website, I noticed that the site uses different domains for the website and email, its policy content still mentions Google+, and key contact and trust information is dispersed across long pages. Domain inconsistency and dated policy language can make a prospective client pause or wonder whether the contact route is current.
@@ -1148,16 +1063,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
+      <c r="H9" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J9" t="str">
         <v>Following up on the Nandy &amp; Co Solicitors website concept</v>
       </c>
-      <c r="K10" t="str" xml:space="preserve">
+      <c r="K9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Nandy &amp; Co team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a consistent branded contact experience, current policies, focused immigration and civil-law pathways, language support and a prominent callback form. This would directly address the current issue: the site uses different domains for the website and email, its policy content still mentions Google+, and key contact and trust information is dispersed across long pages.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1165,62 +1080,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v>Final follow-up — Nandy &amp; Co Solicitors website concept</v>
       </c>
-      <c r="O10" t="str" xml:space="preserve">
+      <c r="O9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Nandy &amp; Co team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S10" t="str">
-        <v>Medium reply potential. Email is published on the official contact page but uses nandysolicitors.co.uk while the website uses nandyandco.co.uk; verify by phone before outreach. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T10" t="str">
-        <v>https://nandyandco.co.uk/contact/ | https://nandyandco.co.uk/privacy-and-cookie-policy/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
         <v>Alexander JLO</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B10" t="str">
         <v>https://www.london-law.co.uk/</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C10" t="str">
         <v>info@london-law.co.uk</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D10" t="str">
         <v>020 7537 7000</v>
       </c>
-      <c r="E11" t="str">
-        <v>LinkedIn: https://www.linkedin.com/company/alexander-jlo | SRA details: https://www.london-law.co.uk/about/</v>
-      </c>
-      <c r="F11" t="str">
+      <c r="E10" t="str" xml:space="preserve">
+        <v xml:space="preserve">LinkedIn: https://www.linkedin.com/company/alexander-jlo
+LinkedIn: https://www.london-law.co.uk/about/</v>
+      </c>
+      <c r="F10" t="str">
         <v>Homepage redesign concept for Alexander JLO</v>
       </c>
-      <c r="G11" t="str" xml:space="preserve">
+      <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Alexander JLO team,
 I found Alexander JLO while researching established London law firms. Your history since 1975 and wide range of personal and commercial services should carry substantial authority online.
 After reviewing the current website, I noticed that the site repeats contact blocks and form elements multiple times, contains generic ‘Menu Item’ labels in navigation output and shows inconsistent copyright ranges across pages. The repetition makes the experience feel longer and less controlled, particularly for a client trying to identify one service and make a confidential enquiry.
@@ -1231,16 +1143,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
+      <c r="H10" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J10" t="str">
         <v>Following up on the Alexander JLO website concept</v>
       </c>
-      <c r="K11" t="str" xml:space="preserve">
+      <c r="K10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Alexander JLO team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a simplified navigation, one clear consultation module, service-specific landing paths, prominent team expertise and current compliance details. This would directly address the current issue: the site repeats contact blocks and form elements multiple times, contains generic ‘Menu Item’ labels in navigation output and shows inconsistent copyright ranges across pages.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1248,62 +1160,60 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>Final follow-up — Alexander JLO website concept</v>
       </c>
-      <c r="O11" t="str" xml:space="preserve">
+      <c r="O10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Alexander JLO team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S11" t="str">
-        <v>High redesign need. Live official site with SRA number and public domain email. General inbox; mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T11" t="str">
-        <v>https://www.london-law.co.uk/ | https://www.london-law.co.uk/about/free-consultation/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
         <v>Akin Palmer LLP</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B11" t="str">
         <v>https://www.akinpalmer.com/</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C11" t="str">
         <v>law@akinpalmer.com</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D11" t="str">
         <v>020 7278 2800</v>
       </c>
-      <c r="E12" t="str">
-        <v>LinkedIn: https://uk.linkedin.com/company/akin-palmer-llp | Facebook: https://www.facebook.com/p/Akin-Palmer-Solicitors-100065357415857/ | SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=521473</v>
-      </c>
-      <c r="F12" t="str">
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Facebook: https://uk.linkedin.com/company/akin-palmer-llp
+Facebook: https://www.facebook.com/p/Akin-Palmer-Solicitors-100065357415857/
+Facebook: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=521473</v>
+      </c>
+      <c r="F11" t="str">
         <v>Homepage redesign concept for Akin Palmer LLP</v>
       </c>
-      <c r="G12" t="str" xml:space="preserve">
+      <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Akin Palmer team,
 I found Akin Palmer LLP while researching established London law firms. Your immigration capability and senior team provide strong material for a credible specialist presentation.
 After reviewing the current website, I noticed that the homepage outputs the full navigation twice, uses broad corporate claims that are not connected to specific client matters and pushes key contact details below lengthy content. A visitor may not quickly understand whether the firm handles their exact immigration problem or who will advise them.
@@ -1314,16 +1224,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
+      <c r="H11" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J11" t="str">
         <v>Following up on the Akin Palmer LLP website concept</v>
       </c>
-      <c r="K12" t="str" xml:space="preserve">
+      <c r="K11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Akin Palmer team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are matter-based immigration choices, solicitor-led proof, a clear assessment process, concise fee context and one visible contact route. This would directly address the current issue: the homepage outputs the full navigation twice, uses broad corporate claims that are not connected to specific client matters and pushes key contact details below lengthy content.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1331,62 +1241,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v>Final follow-up — Akin Palmer LLP website concept</v>
       </c>
-      <c r="O12" t="str" xml:space="preserve">
+      <c r="O11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Akin Palmer team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S12" t="str">
-        <v>High redesign need. Live site, current SRA registration, active company record and domain-matched email. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T12" t="str">
-        <v>https://www.akinpalmer.com/ | https://www.akinpalmer.com/contact/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=521473</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
         <v>Marsans Gitlin Baker</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B12" t="str">
         <v>https://mgb.law/</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C12" t="str">
         <v>email@mgb.law</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D12" t="str">
         <v>020 7499 0620</v>
       </c>
-      <c r="E13" t="str">
-        <v>Instagram: https://www.instagram.com/marsansgitlinbaker/ | SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=565242</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Instagram: https://www.instagram.com/marsansgitlinbaker/
+Instagram: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=565242</v>
+      </c>
+      <c r="F12" t="str">
         <v>Homepage redesign concept for Marsans Gitlin Baker</v>
       </c>
-      <c r="G13" t="str" xml:space="preserve">
+      <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Marsans Gitlin Baker team,
 I found Marsans Gitlin Baker while researching established London law firms. Your established name and broad London legal practice deserve a clear and consistent digital identity.
 After reviewing the current website, I noticed that legacy pages and current pages present different email domains and SRA references, while important services and contact actions compete with repeated footer information. Conflicting legacy details can make clients unsure which contact information is current and can weaken trust in an otherwise established practice.
@@ -1397,16 +1304,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
+      <c r="H12" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J12" t="str">
         <v>Following up on the Marsans Gitlin Baker website concept</v>
       </c>
-      <c r="K13" t="str" xml:space="preserve">
+      <c r="K12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Marsans Gitlin Baker team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are one consistent MGB identity, current regulatory and contact data, clearer service routes, lawyer profiles and a single consultation action. This would directly address the current issue: legacy pages and current pages present different email domains and SRA references, while important services and contact actions compete with repeated footer information.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1414,62 +1321,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <v>Final follow-up — Marsans Gitlin Baker website concept</v>
       </c>
-      <c r="O13" t="str" xml:space="preserve">
+      <c r="O12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Marsans Gitlin Baker team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S13" t="str">
-        <v>Medium reply potential. Current contact page and SRA record match email@mgb.law/SRA 565242; legacy pages should be reviewed before citing exact conflicts. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T13" t="str">
-        <v>https://mgb.law/contact-us/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=565242</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
       </c>
     </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
         <v>Blossom Law Solicitors</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B13" t="str">
         <v>https://blossomlawsolicitors.co.uk/</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C13" t="str">
         <v>info@blossomlawsolicitors.co.uk</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D13" t="str">
         <v>020 7998 1641</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E13" t="str">
         <v>SRA details: https://blossomlawsolicitors.co.uk/website-terms-of-use/</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F13" t="str">
         <v>Homepage redesign concept for Blossom Law Solicitors</v>
       </c>
-      <c r="G14" t="str" xml:space="preserve">
+      <c r="G13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Blossom Law Solicitors team,
 I found Blossom Law Solicitors while researching established London law firms. Your Lexcel accreditation and work across residential property, family and commercial matters are valuable trust signals.
 After reviewing the current website, I noticed that the site still carries a 2018 footer, relies on a dense footer and small quick-link structure, and gives limited visual priority to services, the team or the next step. Clients may miss the firm’s accreditation and expertise because those strengths are not surfaced early enough in the decision journey.
@@ -1480,16 +1383,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
+      <c r="H13" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J13" t="str">
         <v>Following up on the Blossom Law Solicitors website concept</v>
       </c>
-      <c r="K14" t="str" xml:space="preserve">
+      <c r="K13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Blossom Law Solicitors team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a trust-led hero, clear property and family pathways, team profiles, a simple enquiry form and more visible Lexcel and SRA information. This would directly address the current issue: the site still carries a 2018 footer, relies on a dense footer and small quick-link structure, and gives limited visual priority to services, the team or the next step.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1497,62 +1400,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v>Final follow-up — Blossom Law Solicitors website concept</v>
       </c>
-      <c r="O14" t="str" xml:space="preserve">
+      <c r="O13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Blossom Law Solicitors team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S14" t="str">
-        <v>High redesign need. Official terms page publishes the domain email; live firm website displays SRA 565601 and Lexcel. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T14" t="str">
-        <v>https://blossomlawsolicitors.co.uk/ | https://blossomlawsolicitors.co.uk/contact/ | https://blossomlawsolicitors.co.uk/website-terms-of-use/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
         <v>AM International Solicitors</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B14" t="str">
         <v>https://amisolicitors.co.uk/</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C14" t="str">
         <v>anna@amisolicitors.co.uk</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D14" t="str">
         <v>020 3865 1824; WhatsApp 07803 006506</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E14" t="str">
         <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=632695</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F14" t="str">
         <v>Homepage redesign concept for AM International Solicitors</v>
       </c>
-      <c r="G15" t="str" xml:space="preserve">
+      <c r="G14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Anna,
 I found AM International Solicitors while researching established London law firms. Your London and Warsaw presence and cross-border litigation, immigration and business work provide a strong specialist position.
 After reviewing the current website, I noticed that the website carries large blocks of international-service copy, repeats phone and emergency details across pages and gives the consultation form limited guidance about which specialist will respond. International clients may find it difficult to choose the right service or understand the first consultation before submitting personal details.
@@ -1563,16 +1462,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
+      <c r="H14" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J14" t="str">
         <v>Following up on the AM International Solicitors website concept</v>
       </c>
-      <c r="K15" t="str" xml:space="preserve">
+      <c r="K14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Anna,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are country and matter-based routes, a concise international proposition, named specialist cards, a clear WhatsApp action and a guided consultation form. This would directly address the current issue: the website carries large blocks of international-service copy, repeats phone and emergency details across pages and gives the consultation form limited guidance about which specialist will respond.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1580,62 +1479,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <v>Final follow-up — AM International Solicitors website concept</v>
       </c>
-      <c r="O15" t="str" xml:space="preserve">
+      <c r="O14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Anna,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S15" t="str">
-        <v>High reply potential because principal’s named email is published on the official site. Current SRA-regulated firm with active pages. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T15" t="str">
-        <v>https://amisolicitors.co.uk/anna-matelska-principal-managing-director/ | https://amisolicitors.co.uk/contact/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=632695</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
         <v>Broadway Solicitors</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B15" t="str">
         <v>https://broadwaysolicitors.com/</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C15" t="str">
         <v>b.desai@broadwaysolicitors.com</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D15" t="str">
         <v>020 8767 7718; emergency 07957 322868</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E15" t="str">
         <v>SRA details: https://broadwaysolicitors.com/costs/</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F15" t="str">
         <v>Homepage redesign concept for Broadway Solicitors</v>
       </c>
-      <c r="G16" t="str" xml:space="preserve">
+      <c r="G15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bhavna,
 I found Broadway Solicitors while researching established London law firms. Your specialist family, conveyancing and wills practice, together with Lexcel and CQS accreditation, gives clients strong reasons to trust the firm.
 After reviewing the current website, I noticed that the homepage is very sparse, while internal pages duplicate the full navigation and contact blocks and the site still shows a 2017 copyright. The homepage does not explain the depth behind each service, and mobile visitors face a long repeated menu before reaching useful guidance.
@@ -1646,16 +1541,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
+      <c r="H15" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J15" t="str">
         <v>Following up on the Broadway Solicitors website concept</v>
       </c>
-      <c r="K16" t="str" xml:space="preserve">
+      <c r="K15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bhavna,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a clear three-service homepage, visible accreditations, principal-led introduction, matter-specific calls to action, testimonials and a shorter enquiry process. This would directly address the current issue: the homepage is very sparse, while internal pages duplicate the full navigation and contact blocks and the site still shows a 2017 copyright.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1663,62 +1558,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v>Final follow-up — Broadway Solicitors website concept</v>
       </c>
-      <c r="O16" t="str" xml:space="preserve">
+      <c r="O15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bhavna,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S16" t="str">
-        <v>High reply potential because the principal/complaints-handler email is public on the official site. Current SRA 668243 shown. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T16" t="str">
-        <v>https://broadwaysolicitors.com/ | https://broadwaysolicitors.com/contact-us/ | https://broadwaysolicitors.com/terms/complaints-handling-policy/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
         <v>CL Law Solicitors</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B16" t="str">
         <v>https://cllaw.co.uk/</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C16" t="str">
         <v>ulal@cllaw.co.uk</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D16" t="str">
         <v>020 8577 1222</v>
       </c>
-      <c r="E17" t="str">
-        <v>LinkedIn partner: https://uk.linkedin.com/in/hardeep-singh-grewal-4b0478122 | SRA details: https://cllaw.co.uk/contact-us/</v>
-      </c>
-      <c r="F17" t="str">
+      <c r="E16" t="str" xml:space="preserve">
+        <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/in/hardeep-singh-grewal-4b0478122
+LinkedIn: https://cllaw.co.uk/contact-us/</v>
+      </c>
+      <c r="F16" t="str">
         <v>Homepage redesign concept for CL Law Solicitors</v>
       </c>
-      <c r="G17" t="str" xml:space="preserve">
+      <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CL Law team,
 I found CL Law Solicitors while researching established London law firms. Your broad West London practice and long experience across family, property, criminal, immigration and probate matters are strong local credentials.
 After reviewing the current website, I noticed that the site contains visible spelling errors such as ‘Solictors,’ a ‘GDRP Policy’ label, malformed service headings and form validation text such as ‘Invalid Input’ appearing before submission. Visible errors on a legal-services website can undermine confidence in accuracy and may make the enquiry form appear broken.
@@ -1729,16 +1621,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
+      <c r="H16" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J16" t="str">
         <v>Following up on the CL Law Solicitors website concept</v>
       </c>
-      <c r="K17" t="str" xml:space="preserve">
+      <c r="K16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CL Law team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are proofread client-focused copy, corrected policy labels, reliable form states, concise practice pathways, team proof and a clear confidential-enquiry action. This would directly address the current issue: the site contains visible spelling errors such as ‘Solictors,’ a ‘GDRP Policy’ label, malformed service headings and form validation text such as ‘Invalid Input’ appearing before submission.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1746,62 +1638,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v>Final follow-up — CL Law Solicitors website concept</v>
       </c>
-      <c r="O17" t="str" xml:space="preserve">
+      <c r="O16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CL Law team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S17" t="str">
-        <v>High redesign need. Live official site states SRA 565739 and public email. Email is unusual but domain-matched; verify by phone before sending. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T17" t="str">
-        <v>https://cllaw.co.uk/ | https://cllaw.co.uk/contact-us/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
       </c>
     </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
         <v>Right Law</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B17" t="str">
         <v>https://rightlaw.com/</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C17" t="str">
         <v>info@rightlaw.com</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D17" t="str">
         <v>020 3893 3960</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E17" t="str">
         <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=636752</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F17" t="str">
         <v>Homepage redesign concept for Right Law</v>
       </c>
-      <c r="G18" t="str" xml:space="preserve">
+      <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Right Law team,
 I found Right Law while researching established London law firms. Your Barnet location and regulated legal service give local clients a convenient firm to contact.
 After reviewing the current website, I noticed that the site retains an older 2017-era presentation and gives limited prominence to individual lawyer expertise, client proof and the steps after an enquiry. People comparing nearby firms may not see enough evidence or guidance to choose Right Law before they leave the page.
@@ -1812,16 +1700,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
+      <c r="H17" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J17" t="str">
         <v>Following up on the Right Law website concept</v>
       </c>
-      <c r="K18" t="str" xml:space="preserve">
+      <c r="K17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Right Law team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a local trust-led introduction, clear practice cards, named lawyers, transparent first steps, recent testimonials and a prominent consultation action. This would directly address the current issue: the site retains an older 2017-era presentation and gives limited prominence to individual lawyer expertise, client proof and the steps after an enquiry.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1829,62 +1717,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v>Final follow-up — Right Law website concept</v>
       </c>
-      <c r="O18" t="str" xml:space="preserve">
+      <c r="O17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Right Law team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S18" t="str">
-        <v>Medium reply potential. Contact details are corroborated by the SRA and current local business listing; domain email not SMTP-tested.</v>
-      </c>
-      <c r="T18" t="str">
-        <v>https://rightlaw.com/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=636752 | https://www.highstonebusinesscentre.co.uk/</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
         <v>Stevens Machi Solicitors</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B18" t="str">
         <v>https://www.stevensmachi.com/</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C18" t="str">
         <v>info@stevensmachi.com</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D18" t="str">
         <v>020 8318 7768</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E18" t="str">
         <v>SRA details: https://www.stevensmachi.com/contact-us.html</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F18" t="str">
         <v>Homepage redesign concept for Stevens Machi Solicitors</v>
       </c>
-      <c r="G19" t="str" xml:space="preserve">
+      <c r="G18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stevens Machi team,
 I found Stevens Machi Solicitors while researching established London law firms. Your focused immigration practice and experience with appeals, judicial review and complex visa matters are highly marketable strengths.
 After reviewing the current website, I noticed that the enquiry form displays multiple ‘Invalid Input’ messages before a visitor submits anything, the blog’s latest visible articles date from 2017 and the site still uses a long legacy service menu. The form can look broken and the stale news feed may cause clients to question whether the information is current.
@@ -1895,16 +1779,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
+      <c r="H18" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J18" t="str">
         <v>Following up on the Stevens Machi Solicitors website concept</v>
       </c>
-      <c r="K19" t="str" xml:space="preserve">
+      <c r="K18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stevens Machi team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a reliable guided assessment form, current immigration categories, urgent-help route, solicitor profiles, recent insights and a much shorter mobile menu. This would directly address the current issue: the enquiry form displays multiple ‘Invalid Input’ messages before a visitor submits anything, the blog’s latest visible articles date from 2017 and the site still uses a long legacy service menu.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1912,62 +1796,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v>Final follow-up — Stevens Machi Solicitors website concept</v>
       </c>
-      <c r="O19" t="str" xml:space="preserve">
+      <c r="O18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stevens Machi team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S19" t="str">
-        <v>Very high redesign need. Live official site publishes email and SRA 551261. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T19" t="str">
-        <v>https://www.stevensmachi.com/contact-us.html | https://www.stevensmachi.com/Blog/Latest.html</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
         <v>Sacaloffs Solicitors</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B19" t="str">
         <v>https://www.sacaloffs.co.uk/</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C19" t="str">
         <v>info@sacaloffs.co.uk</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D19" t="str">
         <v>020 3457 0932</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E19" t="str">
         <v>SRA details: https://www.sacaloffs.co.uk/Legal.html</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F19" t="str">
         <v>Homepage redesign concept for Sacaloffs Solicitors</v>
       </c>
-      <c r="G20" t="str" xml:space="preserve">
+      <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Roberta,
 I found Sacaloffs Solicitors while researching established London law firms. Your sole-principal model and specialist personal service can be a strong differentiator for clients who want direct senior attention.
 After reviewing the current website, I noticed that the site uses a compact 2016-era layout, small navigation and limited service explanation, with little visual emphasis on your role as sole principal. Potential clients may not immediately understand the personal access and specialist value they receive by instructing your firm.
@@ -1978,16 +1858,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
+      <c r="H19" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J19" t="str">
         <v>Following up on the Sacaloffs Solicitors website concept</v>
       </c>
-      <c r="K20" t="str" xml:space="preserve">
+      <c r="K19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Roberta,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a principal-led hero, focused service pages, a clear consultation process, visible regulatory details and a simple mobile contact action. This would directly address the current issue: the site uses a compact 2016-era layout, small navigation and limited service explanation, with little visual emphasis on your role as sole principal.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -1995,62 +1875,59 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
-      <c r="N20" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v>Final follow-up — Sacaloffs Solicitors website concept</v>
       </c>
-      <c r="O20" t="str" xml:space="preserve">
+      <c r="O19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Roberta,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q20" t="str">
-        <v/>
-      </c>
-      <c r="R20" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S20" t="str">
-        <v>High reply potential because this is a sole-principal practice and the official domain email is public. Site identifies SRA 386312. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T20" t="str">
-        <v>https://www.sacaloffs.co.uk/ | https://www.sacaloffs.co.uk/Legal.html</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
         <v>Rukhsana Hayat &amp; Co Solicitors</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B20" t="str">
         <v>https://www.rukhsanahayat.co.uk/</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C20" t="str">
         <v>info@rukhsanahayat.co.uk</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D20" t="str">
         <v>020 4568 5243; out of hours 07821 539793</v>
       </c>
-      <c r="E21" t="str">
-        <v>LinkedIn: https://uk.linkedin.com/in/rukhsana-hayat-0427b277 | Law Society: https://solicitors.lawsociety.org.uk/office/474730/rukhsana-hayat-co-solicitors</v>
-      </c>
-      <c r="F21" t="str">
+      <c r="E20" t="str" xml:space="preserve">
+        <v xml:space="preserve">LinkedIn: https://uk.linkedin.com/in/rukhsana-hayat-0427b277
+LinkedIn: https://solicitors.lawsociety.org.uk/office/474730/rukhsana-hayat-co-solicitors</v>
+      </c>
+      <c r="F20" t="str">
         <v>Homepage redesign concept for Rukhsana Hayat &amp; Co Solicitors</v>
       </c>
-      <c r="G21" t="str" xml:space="preserve">
+      <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Rukhsana,
 I found Rukhsana Hayat &amp; Co Solicitors while researching established London law firms. Your criminal-defence specialism, out-of-hours arrest support and more than two decades of experience are strong reasons for clients to call.
 After reviewing the current website, I noticed that the website currently says it is under construction and functions mainly as a contact card followed by a long complaints section. Someone needing urgent criminal advice gets little information about offences handled, police-station support, availability or why they should choose the firm.
@@ -2061,16 +1938,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
+      <c r="H20" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J20" t="str">
         <v>Following up on the Rukhsana Hayat &amp; Co Solicitors website concept</v>
       </c>
-      <c r="K21" t="str" xml:space="preserve">
+      <c r="K20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Rukhsana,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a fast urgent-help homepage, one-tap call and WhatsApp actions, clear offence and police-station services, principal credentials and concise compliance pages. This would directly address the current issue: the website currently says it is under construction and functions mainly as a contact card followed by a long complaints section.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -2078,62 +1955,58 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <v>Final follow-up — Rukhsana Hayat &amp; Co Solicitors website concept</v>
       </c>
-      <c r="O21" t="str" xml:space="preserve">
+      <c r="O20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Rukhsana,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S21" t="str">
-        <v>Very high redesign need and high reply potential due to sole-principal contact. Website is live but explicitly under construction. Public domain email; mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T21" t="str">
-        <v>https://www.rukhsanahayat.co.uk/ | https://solicitors.lawsociety.org.uk/office/474730/rukhsana-hayat-co-solicitors</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
         <v>Law Dale Solicitors</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B21" t="str">
         <v>https://lawdalesolicitors.co.uk/</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C21" t="str">
         <v>lawdale2015@hotmail.com</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D21" t="str">
         <v>020 7392 9592</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E21" t="str">
         <v>SRA: https://www.sra.org.uk/consumers/register/organisation/?sraNumber=623543</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F21" t="str">
         <v>Homepage redesign concept for Law Dale Solicitors</v>
       </c>
-      <c r="G22" t="str" xml:space="preserve">
+      <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Law Dale Solicitors team,
 I found Law Dale Solicitors while researching established London law firms. Your East London practice across immigration, family and landlord-and-tenant matters serves clients who need accessible local advice.
 After reviewing the current website, I noticed that the public contact uses a generic Hotmail address rather than the website domain, and the site has limited modern trust, team and enquiry structure. A consumer may hesitate to send confidential details to a free-email address or may struggle to confirm that the website and inbox belong to the same regulated firm.
@@ -2144,16 +2017,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="H22" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
+      <c r="H21" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="J21" t="str">
         <v>Following up on the Law Dale Solicitors website concept</v>
       </c>
-      <c r="K22" t="str" xml:space="preserve">
+      <c r="K21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Law Dale Solicitors team,
 I wanted to follow up on the homepage concept I sent. The first changes I would prioritise are a domain-based contact route, visible regulated-team profiles, clear service choices, multilingual support information and a secure guided enquiry form. This would directly address the current issue: the public contact uses a generic Hotmail address rather than the website domain, and the site has limited modern trust, team and enquiry structure.
 To keep the project low-risk, most redesigns of this size fall between US$200 and US$800 as a one-time cost, depending on the final number of pages and features. We would agree the exact scope and price first. You would not pay upfront; payment would be due only after the website is delivered, reviewed and approved. Hosting, domain renewal and any paid third-party services would be separate only if required.
@@ -2161,51 +2034,47 @@
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="L22" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v>Final follow-up — Law Dale Solicitors website concept</v>
       </c>
-      <c r="O22" t="str" xml:space="preserve">
+      <c r="O21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Law Dale Solicitors team,
 Just a final follow-up about the redesign concept. The main opportunity is still to make the firm’s expertise easier to understand and the enquiry route easier to use, especially on mobile.
 If a redesign is not a priority now, no problem at all. If it is useful, reply with “plan” and I will send a concise recommended scope, timeline and fixed price with no obligation.
 Kind regards,
 Khaled Saifullah
 Web Developer
-Portfolio: ksnirob.com</v>
-      </c>
-      <c r="P22" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v>Qualified</v>
-      </c>
-      <c r="S22" t="str">
-        <v>Medium reply potential. SRA currently lists the Hotmail address and website together, so identity is corroborated, but verify by phone before sending attachments. Mailbox not SMTP-tested.</v>
-      </c>
-      <c r="T22" t="str">
-        <v>https://lawdalesolicitors.co.uk/ | https://www.sra.org.uk/consumers/register/organisation/?sraNumber=623543</v>
+Portfolio: ksnirob.com
+The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H3:H1000 L3:L1000 P3:P1000">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
       <formula1>"Draft,Sent,Replied,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R3:R1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/Batch_05_Leads_Tracker.xlsx
+++ b/excel/Batch_05_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/excel/Batch_05_Leads_Tracker.xlsx
+++ b/excel/Batch_05_Leads_Tracker.xlsx
@@ -527,10 +527,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N2" t="str">
         <v>Final follow-up — R.O.C.K Solicitors website concept</v>
@@ -607,10 +607,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N3" t="str">
         <v>Final follow-up — Pearl &amp; Co Solicitors website concept</v>
@@ -686,10 +686,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N4" t="str">
         <v>Final follow-up — A.T. Law website concept</v>
@@ -767,10 +767,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N5" t="str">
         <v>Final follow-up — Douglass Simon Solicitors website concept</v>
@@ -846,10 +846,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N6" t="str">
         <v>Final follow-up — Mono Law website concept</v>
@@ -925,10 +925,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N7" t="str">
         <v>Final follow-up — Ties Solicitors website concept</v>
@@ -1005,10 +1005,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N8" t="str">
         <v>Final follow-up — Tice Madox website concept</v>
@@ -1084,10 +1084,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N9" t="str">
         <v>Final follow-up — Nandy &amp; Co Solicitors website concept</v>
@@ -1164,10 +1164,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N10" t="str">
         <v>Final follow-up — Alexander JLO website concept</v>
@@ -1245,10 +1245,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N11" t="str">
         <v>Final follow-up — Akin Palmer LLP website concept</v>
@@ -1325,10 +1325,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N12" t="str">
         <v>Final follow-up — Marsans Gitlin Baker website concept</v>
@@ -1404,10 +1404,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N13" t="str">
         <v>Final follow-up — Blossom Law Solicitors website concept</v>
@@ -1483,10 +1483,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N14" t="str">
         <v>Final follow-up — AM International Solicitors website concept</v>
@@ -1562,10 +1562,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N15" t="str">
         <v>Final follow-up — Broadway Solicitors website concept</v>
@@ -1642,10 +1642,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N16" t="str">
         <v>Final follow-up — CL Law Solicitors website concept</v>
@@ -1721,10 +1721,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N17" t="str">
         <v>Final follow-up — Right Law website concept</v>
@@ -1800,10 +1800,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N18" t="str">
         <v>Final follow-up — Stevens Machi Solicitors website concept</v>
@@ -1879,10 +1879,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N19" t="str">
         <v>Final follow-up — Sacaloffs Solicitors website concept</v>
@@ -1959,10 +1959,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N20" t="str">
         <v>Final follow-up — Rukhsana Hayat &amp; Co Solicitors website concept</v>
@@ -2038,10 +2038,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-14</v>
       </c>
       <c r="N21" t="str">
         <v>Final follow-up — Law Dale Solicitors website concept</v>

--- a/excel/Batch_05_Leads_Tracker.xlsx
+++ b/excel/Batch_05_Leads_Tracker.xlsx
@@ -2072,7 +2072,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>
